--- a/agriculture 15.xlsx
+++ b/agriculture 15.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t xml:space="preserve">2020-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <r>
@@ -290,7 +293,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source: </t>
     </r>
@@ -300,7 +302,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">EPWRF(Economic &amp; Political Weekly Research Foundation) 1950-2021</t>
     </r>
@@ -313,7 +314,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description</t>
     </r>
@@ -323,7 +323,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> : Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -337,7 +336,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -368,11 +367,17 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -456,11 +461,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -481,8 +486,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AC62"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.14"/>
@@ -5322,63 +5327,110 @@
         <v>4.04875124673831</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-    </row>
-    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+    </row>
+    <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
-      <c r="N61" s="7"/>
-      <c r="O61" s="7"/>
-      <c r="P61" s="7"/>
-      <c r="Q61" s="7"/>
-      <c r="R61" s="7"/>
-      <c r="S61" s="7"/>
-      <c r="T61" s="7"/>
-      <c r="U61" s="7"/>
-      <c r="V61" s="7"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="6"/>
+      <c r="U61" s="6"/>
+      <c r="V61" s="6"/>
+      <c r="W61" s="6"/>
+      <c r="X61" s="6"/>
+      <c r="Y61" s="6"/>
+      <c r="Z61" s="6"/>
+      <c r="AA61" s="6"/>
+      <c r="AB61" s="6"/>
+      <c r="AC61" s="6"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
+      <c r="R62" s="7"/>
+      <c r="S62" s="7"/>
+      <c r="T62" s="7"/>
+      <c r="U62" s="7"/>
+      <c r="V62" s="7"/>
+      <c r="W62" s="7"/>
+      <c r="X62" s="7"/>
+      <c r="Y62" s="7"/>
+      <c r="Z62" s="7"/>
+      <c r="AA62" s="7"/>
+      <c r="AB62" s="7"/>
+      <c r="AC62" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A60:V60"/>
-    <mergeCell ref="A61:V61"/>
+  <mergeCells count="3">
+    <mergeCell ref="A60:AC60"/>
+    <mergeCell ref="A61:AC61"/>
+    <mergeCell ref="A62:AC62"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 15.xlsx
+++ b/agriculture 15.xlsx
@@ -283,7 +283,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <r>
@@ -293,6 +293,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source: </t>
     </r>
@@ -302,6 +303,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">EPWRF(Economic &amp; Political Weekly Research Foundation) 1950-2021</t>
     </r>
@@ -314,6 +316,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description</t>
     </r>
@@ -323,6 +326,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> : Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -336,7 +340,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -367,17 +371,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -436,7 +434,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -461,11 +459,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -487,7 +489,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AC62"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.14"/>
@@ -5328,103 +5330,103 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="3"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
-      <c r="AB60" s="3"/>
-      <c r="AC60" s="3"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6"/>
+      <c r="V60" s="6"/>
+      <c r="W60" s="6"/>
+      <c r="X60" s="6"/>
+      <c r="Y60" s="6"/>
+      <c r="Z60" s="6"/>
+      <c r="AA60" s="6"/>
+      <c r="AB60" s="6"/>
+      <c r="AC60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="6"/>
-      <c r="T61" s="6"/>
-      <c r="U61" s="6"/>
-      <c r="V61" s="6"/>
-      <c r="W61" s="6"/>
-      <c r="X61" s="6"/>
-      <c r="Y61" s="6"/>
-      <c r="Z61" s="6"/>
-      <c r="AA61" s="6"/>
-      <c r="AB61" s="6"/>
-      <c r="AC61" s="6"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="7"/>
+      <c r="O61" s="7"/>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7"/>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="7"/>
+      <c r="AA61" s="7"/>
+      <c r="AB61" s="7"/>
+      <c r="AC61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="7"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="7"/>
-      <c r="T62" s="7"/>
-      <c r="U62" s="7"/>
-      <c r="V62" s="7"/>
-      <c r="W62" s="7"/>
-      <c r="X62" s="7"/>
-      <c r="Y62" s="7"/>
-      <c r="Z62" s="7"/>
-      <c r="AA62" s="7"/>
-      <c r="AB62" s="7"/>
-      <c r="AC62" s="7"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="8"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="8"/>
+      <c r="R62" s="8"/>
+      <c r="S62" s="8"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="8"/>
+      <c r="V62" s="8"/>
+      <c r="W62" s="8"/>
+      <c r="X62" s="8"/>
+      <c r="Y62" s="8"/>
+      <c r="Z62" s="8"/>
+      <c r="AA62" s="8"/>
+      <c r="AB62" s="8"/>
+      <c r="AC62" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
